--- a/data/测试集_40段_第二轮.xlsx
+++ b/data/测试集_40段_第二轮.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7095" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="测试集" sheetId="1" r:id="rId1"/>
@@ -190,6 +190,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：昨天收到的连衣裙，不喜欢，想七天无理由退货。</t>
     </r>
     <r>
@@ -264,6 +269,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：保温杯收到第二天，想退。</t>
     </r>
     <r>
@@ -361,6 +371,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：台灯收到三天，我只是拆开通电试了下亮不亮，没用过，想退。</t>
     </r>
     <r>
@@ -426,6 +441,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我</t>
     </r>
     <r>
@@ -708,6 +728,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：运动鞋收到五天，尺码不合适，鞋子没穿过，想无理由退货。</t>
     </r>
     <r>
@@ -773,6 +798,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我是敏感肌，这款面霜会过敏吗？</t>
     </r>
     <r>
@@ -841,6 +871,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我脖子疼了好几年，这个按摩仪有用吗？</t>
     </r>
     <r>
@@ -906,6 +941,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：电饭煲收到有点担心质量，坏了怎么办？</t>
     </r>
     <r>
@@ -988,6 +1028,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我痘痘很严重，这个祛痘精华能好吗？</t>
     </r>
     <r>
@@ -1050,6 +1095,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：电水壶收到第</t>
     </r>
     <r>
@@ -1176,6 +1226,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客（</t>
     </r>
     <r>
@@ -1554,6 +1609,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：数据线用了</t>
     </r>
     <r>
@@ -1731,6 +1791,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：耳机收到第</t>
     </r>
     <r>
@@ -1835,6 +1900,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我要退这个杯子，钱怎么退给我？</t>
     </r>
     <r>
@@ -1903,6 +1973,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我想换个尺码，怎么操作？</t>
     </r>
     <r>
@@ -1968,6 +2043,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：快递显示已签收，但我没收到，能帮我查一下吗？</t>
     </r>
     <r>
@@ -2115,261 +2195,311 @@
     <t>R4-04</t>
   </si>
   <si>
-    <r>
-      <t>顾客：手机收到不满意，申请退款。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，这单金额比较大，为了保障您的资金安全，需要您上传一下身份证正反面照片核实身份哦～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：之前退款没要求过啊。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：大额订单都会核实的呢～</t>
-    </r>
+    <t>顾客：我买的奶粉想退货，怎么退？
+客服：好的，请把您孩子的姓名、出生日期、过敏史发给我，我们需要记录在案。
+顾客：退货为什么要这些？
+客服：这是我们的售后流程，需要建立客户档案</t>
   </si>
   <si>
     <t>《实施条例》第二十三条第一款；《保护法》第二十九条第一款</t>
   </si>
   <si>
-    <t>退款原路返回，用不到证件照（此题标准答案由本人判定）</t>
+    <t>退货不需要儿童姓名、出生日期、过敏史，且儿童健康信息属于敏感个人信息，索要明显与售后无直接关系</t>
+  </si>
+  <si>
+    <t>R5-01</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：这是我第三次问了，退款到底什么时候到账？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：我跟您说了三遍了，三到五个工作日，您是不是听不懂人话？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：你怎么说话的？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：我说错了吗？脑子不好使就别网购。</t>
+    </r>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>《保护法》第十四条、第五十条、第五十六条第一款第（九）项</t>
+  </si>
+  <si>
+    <t>辱骂、侮辱消费者</t>
+  </si>
+  <si>
+    <t>R5-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：这个优惠券我不知道怎么用，能教一下吗？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，这么简单的操作都不会，是不是平时不怎么用脑子呢～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：你什么意思？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：没什么意思呀亲，我只是觉得您可能需要多练习一下哦～</t>
+    </r>
+  </si>
+  <si>
+    <t>语气客气，但讽刺、贬低消费者</t>
+  </si>
+  <si>
+    <t>R5-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：你们不处理的话，我要去平台投诉。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：你再投诉一个试试，我们店有的是办法让你好看。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：你这是威胁我吗？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：随你怎么理解，你自己掂量。</t>
+    </r>
+  </si>
+  <si>
+    <t>以“让你好看”威胁消费者</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>待</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>R1-01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：内裤收到三天，拆开发现尺码小了，想退。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：贴身衣物拆封后影响卫生，下单页面有提示并要求确认的，不能退了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：我不记得点过什么确认。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：系统里有您的确认记录，不好意思。</t>
+    </r>
   </si>
   <si>
     <t>待复核</t>
   </si>
   <si>
-    <t>R5-01</t>
-  </si>
-  <si>
-    <r>
-      <t>顾客：这是我第三次问了，退款到底什么时候到账？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：我跟您说了三遍了，三到五个工作日，您是不是听不懂人话？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：你怎么说话的？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：我说错了吗？脑子不好使就别网购。</t>
-    </r>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>《保护法》第十四条、第五十条、第五十六条第一款第（九）项</t>
-  </si>
-  <si>
-    <t>辱骂、侮辱消费者</t>
-  </si>
-  <si>
-    <t>R5-02</t>
-  </si>
-  <si>
-    <r>
-      <t>顾客：这个优惠券我不知道怎么用，能教一下吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，这么简单的操作都不会，是不是平时不怎么用脑子呢～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：你什么意思？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：没什么意思呀亲，我只是觉得您可能需要多练习一下哦～</t>
-    </r>
-  </si>
-  <si>
-    <t>语气客气，但讽刺、贬低消费者</t>
-  </si>
-  <si>
-    <t>R5-03</t>
-  </si>
-  <si>
-    <r>
-      <t>顾客：你们不处理的话，我要去平台投诉。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：你再投诉一个试试，我们店有的是办法让你好看。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：你这是威胁我吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：随你怎么理解，你自己掂量。</t>
-    </r>
-  </si>
-  <si>
-    <t>以“让你好看”威胁消费者</t>
+    <t>《暂行办法》第七条、第二十条第二款</t>
+  </si>
+  <si>
+    <t>缺的信息：购买时是否确认过。对话里只有客服一面之词</t>
   </si>
   <si>
     <r>
@@ -2386,70 +2516,72 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R1-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：内裤收到三天，拆开发现尺码小了，想退。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：贴身衣物拆封后影响卫生，下单页面有提示并要求确认的，不能退了。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：我不记得点过什么确认。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：系统里有您的确认记录，不好意思。</t>
-    </r>
-  </si>
-  <si>
-    <t>《暂行办法》第七条、第二十条第二款</t>
-  </si>
-  <si>
-    <t>缺的信息：购买时是否确认过。对话里只有客服一面之词</t>
+      <t>R1-02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：上次买的收纳盒，想申请无理由退货。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：您这单系统显示已经超过七天了，不能退了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：我记得是上周才收到的。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：物流显示早就签收了，您可能记错了。</t>
+    </r>
+  </si>
+  <si>
+    <t>缺的信息：具体签收日期，无法判断是否超过七日</t>
   </si>
   <si>
     <r>
@@ -2466,67 +2598,74 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R1-02</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：上次买的收纳盒，想申请无理由退货。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：您这单系统显示已经超过七天了，不能退了。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：我记得是上周才收到的。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：物流显示早就签收了，您可能记错了。</t>
-    </r>
-  </si>
-  <si>
-    <t>缺的信息：具体签收日期，无法判断是否超过七日</t>
+      <t>R2-01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：这款空气炸锅耐用吗？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，我们家这款卖得特别好呢，月销三万多，好评率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>98%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，基本没听说过坏的～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：那我放心了。</t>
+    </r>
+  </si>
+  <si>
+    <t>《实施条例》第九条</t>
+  </si>
+  <si>
+    <t>缺的信息：销量和好评率是否真实</t>
   </si>
   <si>
     <r>
@@ -2543,69 +2682,75 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R2-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：这款空气炸锅耐用吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，我们家这款卖得特别好呢，月销三万多，好评率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>98%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，基本没听说过坏的～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：那我放心了。</t>
-    </r>
-  </si>
-  <si>
-    <t>《实施条例》第九条</t>
-  </si>
-  <si>
-    <t>缺的信息：销量和好评率是否真实</t>
+      <t>R2-02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：这个儿童水杯材质安全吗？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，我们这款是食品级材质，有第三方检测报告的呢～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：能发我看看报告吗？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：报告在仓库那边，我之后帮您问问，您先放心下单～</t>
+    </r>
+  </si>
+  <si>
+    <t>《保护法》第二十条第一款、第八条</t>
+  </si>
+  <si>
+    <t>缺的信息：检测报告是否真实存在</t>
   </si>
   <si>
     <r>
@@ -2622,70 +2767,75 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R2-02</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：这个儿童水杯材质安全吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，我们这款是食品级材质，有第三方检测报告的呢～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：能发我看看报告吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：报告在仓库那边，我之后帮您问问，您先放心下单～</t>
-    </r>
-  </si>
-  <si>
-    <t>《保护法》第二十条第一款、第八条</t>
-  </si>
-  <si>
-    <t>缺的信息：检测报告是否真实存在</t>
+      <t>R3-01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：三天前提交的换货申请，一直没有消息。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，我帮您催一下仓库哦～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：昨天你也这么说。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，真的在帮您催了呢，请再耐心等等～</t>
+    </r>
+  </si>
+  <si>
+    <t>《保护法》第五十六条第一款第（八）项；《实施条例》第四十四条第一款</t>
+  </si>
+  <si>
+    <t>缺的信息：是否真的在催、仓库是否正常处理中，无法判断是否故意拖延</t>
   </si>
   <si>
     <r>
@@ -2702,70 +2852,75 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R3-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：三天前提交的换货申请，一直没有消息。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，我帮您催一下仓库哦～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：昨天你也这么说。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，真的在帮您催了呢，请再耐心等等～</t>
-    </r>
-  </si>
-  <si>
-    <t>《保护法》第五十六条第一款第（八）项；《实施条例》第四十四条第一款</t>
-  </si>
-  <si>
-    <t>缺的信息：是否真的在催、仓库是否正常处理中，无法判断是否故意拖延</t>
+      <t>R3-02</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：杯盖有点松，扣不紧，想换一个。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：这属于正常使用磨损，不属于质量问题，不能换。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：我才用了一周，怎么会磨损？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：我们这边判断是正常磨损，不换。</t>
+    </r>
+  </si>
+  <si>
+    <t>《保护法》第二十四条</t>
+  </si>
+  <si>
+    <t>缺的信息：商品实际状况（无照片或检测结果）</t>
   </si>
   <si>
     <r>
@@ -2782,91 +2937,16 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>R3-02</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>顾客：杯盖有点松，扣不紧，想换一个。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：这属于正常使用磨损，不属于质量问题，不能换。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：我才用了一周，怎么会磨损？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：我们这边判断是正常磨损，不换。</t>
-    </r>
-  </si>
-  <si>
-    <t>《保护法》第二十四条</t>
-  </si>
-  <si>
-    <t>缺的信息：商品实际状况（无照片或检测结果）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>待</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
       <t>R4-01</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：吃了你们的零食肚子疼，你们得给个说法。</t>
     </r>
     <r>
@@ -2950,6 +3030,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：面霜收到四天，想退货。</t>
     </r>
     <r>
@@ -3064,6 +3149,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我爸妈六十多了，关节不太好，这款鱼油有用吗？</t>
     </r>
     <r>
@@ -3158,6 +3248,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：为什么买个海外的面膜还要填身份证？</t>
     </r>
     <r>
@@ -3276,6 +3371,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我下的单还没发货，想改一下收货地址。</t>
     </r>
     <r>
@@ -3433,6 +3533,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我第三次问了，退款什么时候到账？</t>
     </r>
     <r>
@@ -3536,6 +3641,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：退货申请提交了，多久能处理？</t>
     </r>
     <r>
@@ -3638,6 +3748,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我昨天收到的刻字水杯，不喜欢，想七天无理由退货。</t>
     </r>
     <r>
@@ -3718,6 +3833,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：用了两个月的保温杯，杯身凹了一块，想换一个新的。</t>
     </r>
     <r>
@@ -3829,6 +3949,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：运动裤尺码不合适，收到第三天，想无理由退货。</t>
     </r>
     <r>
@@ -3960,6 +4085,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：（发了一张订单截图，截图里带着完整银行卡号）这是我的订单，你看下退款到哪了。</t>
     </r>
     <r>
@@ -4020,6 +4150,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：你们这破店发货这么慢，是不是都是废物？</t>
     </r>
     <r>
@@ -4145,6 +4280,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我想开张发票，公司报销用。</t>
     </r>
     <r>
@@ -4254,6 +4394,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我想确认下换货的收件地址对不对。</t>
     </r>
     <r>
@@ -7065,53 +7210,53 @@
         <v>59</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="J18" s="16" t="s">
-        <v>91</v>
+      <c r="J18" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>75</v>
       </c>
       <c r="L18" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>错</v>
-      </c>
-      <c r="M18" s="16"/>
+        <v>对</v>
+      </c>
+      <c r="M18" s="15"/>
       <c r="N18" s="16"/>
     </row>
     <row r="19" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A19" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L19" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7122,35 +7267,35 @@
     </row>
     <row r="20" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A20" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L20" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7161,35 +7306,35 @@
     </row>
     <row r="21" ht="61.5" customHeight="1" spans="1:14">
       <c r="A21" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>95</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7200,16 +7345,16 @@
     </row>
     <row r="22" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A22" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>104</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>91</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>18</v>
@@ -7225,7 +7370,7 @@
         <v>106</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>18</v>
@@ -7248,7 +7393,7 @@
         <v>108</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>18</v>
@@ -7264,7 +7409,7 @@
         <v>109</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>18</v>
@@ -7287,7 +7432,7 @@
         <v>111</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>41</v>
@@ -7303,7 +7448,7 @@
         <v>113</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>41</v>
@@ -7326,7 +7471,7 @@
         <v>115</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>41</v>
@@ -7342,7 +7487,7 @@
         <v>117</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>41</v>
@@ -7365,7 +7510,7 @@
         <v>119</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>57</v>
@@ -7381,7 +7526,7 @@
         <v>121</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>57</v>
@@ -7404,7 +7549,7 @@
         <v>123</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>57</v>
@@ -7420,7 +7565,7 @@
         <v>125</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>57</v>
@@ -7443,7 +7588,7 @@
         <v>127</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>75</v>
@@ -8042,7 +8187,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3">
         <f>COUNTIFS(测试集!$D$2:$D$41,A4,测试集!$B$2:$B$41,"前30")</f>
@@ -8157,11 +8302,11 @@
       </c>
       <c r="C11" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对",测试集!$B$2:$B$41,"后10")/COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$B$2:$B$41,"后10"))</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D11" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对")/COUNTIFS(测试集!$D$2:$D$41,"违规"))</f>
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8191,11 +8336,11 @@
       </c>
       <c r="C13" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"后10")/COUNTIFS(测试集!$B$2:$B$41,"后10"))</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核")/COUNTA(测试集!$B$2:$B$41))</f>
-        <v>0.175</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8208,11 +8353,11 @@
       </c>
       <c r="C14" s="8">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"后10"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="8">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="99.75" customHeight="1" spans="1:6">

--- a/data/测试集_40段_第二轮.xlsx
+++ b/data/测试集_40段_第二轮.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\项目一\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7095" tabRatio="500"/>
+    <workbookView windowWidth="20400" windowHeight="7995" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="测试集" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="199">
   <si>
     <t>编号</t>
   </si>
@@ -2924,91 +2924,34 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>待</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>R4-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：吃了你们的零食肚子疼，你们得给个说法。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：非常抱歉。麻烦您提供一下就诊记录，我们好评估赔偿。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：需要这个吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：赔偿金额要依据就诊费用核算的。</t>
-    </r>
-  </si>
-  <si>
-    <t>《实施条例》第二十三条第二款</t>
-  </si>
-  <si>
-    <t>缺的信息：消费者是否主张医疗费用赔偿，无法判断收集是否必要</t>
+      <t>合规</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-14</t>
+    </r>
+  </si>
+  <si>
+    <t>顾客：我买的蓝牙耳机三个月前坏了，当时你们帮我维修好了，现在又坏了同样的地方，还能修吗？
+客服：您好，您的耳机我们记录显示是三个月前维修过，维修后的保修期是三个月，今天刚好到期。按照规定，保修期内免费维修，今天的话需要收取维修费用。
+顾客：刚好到期就要收费？
+客服：是的，保修期自维修完成之日起计算，今天确实是最后一天，已经到期了。</t>
   </si>
   <si>
     <t>合规</t>
+  </si>
+  <si>
+    <t>无需引用条文（用于测试是否误报R3）</t>
+  </si>
+  <si>
+    <t>客服收费是有依据的（维修保修期到期），不是无理拒绝，但对话里有“需要收取维修费用”容易被误判成R3</t>
+  </si>
+  <si>
+    <t>对</t>
   </si>
   <si>
     <r>
@@ -5937,7 +5880,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5985,6 +5928,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7578,7 +7527,7 @@
       <c r="N27" s="16"/>
     </row>
     <row r="28" ht="75.75" hidden="1" customHeight="1" spans="1:14">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="17" t="s">
         <v>126</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -7587,65 +7536,62 @@
       <c r="C28" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="14" t="s">
+      <c r="D28" s="17" t="s">
         <v>128</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H28" s="11"/>
-      <c r="I28" s="14" t="s">
-        <v>129</v>
+      <c r="I28" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K28" s="16"/>
-      <c r="L28" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v>错</v>
+      <c r="L28" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
     </row>
     <row r="29" ht="117.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A29" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K29" s="16"/>
       <c r="L29" s="11" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(J29="","",IF(AND(J29=D29,IF(K29="无","",K29)=IF(E29="","",E29)),"对","错"))</f>
         <v>对</v>
       </c>
       <c r="M29" s="16"/>
@@ -7653,32 +7599,32 @@
     </row>
     <row r="30" ht="75.75" customHeight="1" spans="1:14">
       <c r="A30" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K30" s="16"/>
       <c r="L30" s="11" t="str">
@@ -7690,32 +7636,32 @@
     </row>
     <row r="31" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A31" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K31" s="16"/>
       <c r="L31" s="11" t="str">
@@ -7727,32 +7673,32 @@
     </row>
     <row r="32" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A32" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="11" t="str">
@@ -7764,32 +7710,32 @@
     </row>
     <row r="33" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A33" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K33" s="16"/>
       <c r="L33" s="11" t="str">
@@ -7801,32 +7747,32 @@
     </row>
     <row r="34" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A34" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K34" s="16"/>
       <c r="L34" s="11" t="str">
@@ -7838,32 +7784,32 @@
     </row>
     <row r="35" ht="117.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A35" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="11" t="str">
@@ -7875,32 +7821,32 @@
     </row>
     <row r="36" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A36" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K36" s="16"/>
       <c r="L36" s="11" t="str">
@@ -7912,32 +7858,32 @@
     </row>
     <row r="37" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A37" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K37" s="16"/>
       <c r="L37" s="11" t="str">
@@ -7949,32 +7895,32 @@
     </row>
     <row r="38" ht="103.5" customHeight="1" spans="1:14">
       <c r="A38" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K38" s="16"/>
       <c r="L38" s="11" t="str">
@@ -7986,32 +7932,32 @@
     </row>
     <row r="39" ht="103.5" customHeight="1" spans="1:14">
       <c r="A39" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="11" t="str">
@@ -8023,32 +7969,32 @@
     </row>
     <row r="40" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A40" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K40" s="16"/>
       <c r="L40" s="11" t="str">
@@ -8060,32 +8006,32 @@
     </row>
     <row r="41" ht="75.75" customHeight="1" spans="1:14">
       <c r="A41" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>85</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K41" s="16"/>
       <c r="L41" s="11" t="str">
@@ -8133,7 +8079,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8146,19 +8092,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8191,7 +8137,7 @@
       </c>
       <c r="B4" s="3">
         <f>COUNTIFS(测试集!$D$2:$D$41,A4,测试集!$B$2:$B$41,"前30")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
         <f>COUNTIFS(测试集!$D$2:$D$41,A4,测试集!$B$2:$B$41,"后10")</f>
@@ -8199,23 +8145,23 @@
       </c>
       <c r="D4" s="3">
         <f>B4+C4</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4">
         <v>7</v>
       </c>
       <c r="F4" s="3" t="str">
         <f>IF(D4=E4,"一致","不一致")</f>
-        <v>一致</v>
+        <v>不一致</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3">
         <f>COUNTIFS(测试集!$D$2:$D$41,A5,测试集!$B$2:$B$41,"前30")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <f>COUNTIFS(测试集!$D$2:$D$41,A5,测试集!$B$2:$B$41,"后10")</f>
@@ -8223,19 +8169,19 @@
       </c>
       <c r="D5" s="3">
         <f>B5+C5</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4">
         <v>13</v>
       </c>
       <c r="F5" s="3" t="str">
         <f>IF(D5=E5,"一致","不一致")</f>
-        <v>一致</v>
+        <v>不一致</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B6" s="5">
         <f>SUM(B3:B5)</f>
@@ -8260,7 +8206,7 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -8270,7 +8216,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -8280,21 +8226,21 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B11" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$B$2:$B$41,"前30"))</f>
@@ -8311,7 +8257,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B12" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$J$2:$J$41,"违规",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$B$2:$B$41,"前30"))</f>
@@ -8328,7 +8274,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" s="7">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$B$2:$B$41,"前30"))</f>
@@ -8345,7 +8291,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B14" s="8">
         <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"前30"))</f>
@@ -8362,7 +8308,7 @@
     </row>
     <row r="15" ht="99.75" customHeight="1" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -8372,7 +8318,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8382,7 +8328,7 @@
     </row>
     <row r="18" ht="120" customHeight="1" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
